--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_35.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1728492.386273655</v>
+        <v>1720570.097537048</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7154817.0307476</v>
+        <v>7149301.31357588</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7154817.0307476</v>
+        <v>7149301.31357588</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1421810.501097731</v>
+        <v>1426871.010043778</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1421810.501097731</v>
+        <v>1426871.010043778</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18751487.34853294</v>
+        <v>18748798.59238384</v>
       </c>
     </row>
   </sheetData>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>28.70619138541469</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>96.38875918773755</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>332.0195022027714</v>
+        <v>135.3518862151733</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>385</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21.95645751172319</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -857,7 +857,7 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q4" t="n">
-        <v>325.839266425598</v>
+        <v>320.6301239373217</v>
       </c>
       <c r="R4" t="n">
         <v>326.6021279811511</v>
@@ -897,7 +897,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>39.04534712526427</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>32.58699138541454</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>159.6473895655479</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>385</v>
+        <v>165.8545209174294</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>386</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1131,7 +1131,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>78.1807696284084</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>32.58699138541447</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1258,22 +1258,22 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>188.6630309849417</v>
+        <v>386</v>
       </c>
       <c r="T9" t="n">
-        <v>5.357765217513816</v>
+        <v>211.4793023791269</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>385</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>385</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1386,7 +1386,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>291.8106252399262</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M13" t="n">
-        <v>295.6316114025499</v>
+        <v>147.3731072710768</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.87244134606632</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>188.5028512606473</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>208.5472557260005</v>
+        <v>342.1496093272373</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>178.7573722870162</v>
+        <v>184.2505648441361</v>
       </c>
       <c r="H17" t="n">
         <v>183.0096587035274</v>
@@ -1890,7 +1890,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S17" t="n">
-        <v>275.3413603594427</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>361.6755817285639</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2036,19 +2036,19 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>207.1744458872908</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>84.90775442161444</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>25.87859882829446</v>
+        <v>31.37179138541422</v>
       </c>
       <c r="S20" t="n">
         <v>269.8481678023229</v>
@@ -2136,7 +2136,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V20" t="n">
-        <v>410.344216723944</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W20" t="n">
         <v>413.3734759809475</v>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>345.9207354288559</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>48.91631418759636</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>25.87859882829446</v>
+        <v>31.37179138541422</v>
       </c>
       <c r="S23" t="n">
         <v>269.8481678023229</v>
@@ -2379,7 +2379,7 @@
         <v>413.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>372.7750260177875</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y23" t="n">
         <v>286.3174326828064</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>278.3114466390653</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>344.5479255901462</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="26">
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>257.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>229.9677708001137</v>
+        <v>225.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>186.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>180.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>180.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>201.296964844136</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>184.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,28 +2598,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>25.87859882829446</v>
+        <v>26.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>270.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>362.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>424.2212965486107</v>
+        <v>425.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>405.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>413.3734759809475</v>
+        <v>414.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>367.2818334606677</v>
+        <v>368.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>287.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>159.5565566463266</v>
+        <v>160.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>136.0999124455193</v>
+        <v>137.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>122.9376868977026</v>
+        <v>123.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>117.6720972219126</v>
+        <v>118.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>114.6362423378769</v>
+        <v>115.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>100.7395358750273</v>
+        <v>101.7395358750273</v>
       </c>
       <c r="H27" t="n">
-        <v>107.1680871864211</v>
+        <v>108.1680871864211</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>322.2737972923793</v>
+        <v>323.2737972923793</v>
       </c>
       <c r="S27" t="n">
-        <v>241.5639999646113</v>
+        <v>242.5639999646113</v>
       </c>
       <c r="T27" t="n">
-        <v>180.3577652175138</v>
+        <v>181.3577652175138</v>
       </c>
       <c r="U27" t="n">
-        <v>175.2103597601867</v>
+        <v>176.2103597601867</v>
       </c>
       <c r="V27" t="n">
-        <v>189.5106671915202</v>
+        <v>190.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>207.3731429098285</v>
+        <v>208.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>194.8627394453875</v>
+        <v>195.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>174.3913927661343</v>
+        <v>175.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>48.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>61.53621805555548</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>4.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2753,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>225.9876446236372</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>190.8323482969696</v>
       </c>
       <c r="E29" t="n">
         <v>179.3632896068686</v>
@@ -2802,7 +2802,7 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>184.2505648441361</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
         <v>183.0096587035274</v>
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>294.4243626791926</v>
+        <v>344.5479255901462</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>256.9993129555745</v>
+        <v>262.4925055126944</v>
       </c>
       <c r="C32" t="n">
         <v>224.4745782429939</v>
@@ -3075,7 +3075,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S32" t="n">
-        <v>275.3413603594427</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T32" t="n">
         <v>361.6755817285639</v>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3212,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>146.0002974323671</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3343,7 +3343,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>11.09991244551929</v>
+        <v>75.83998807325933</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -3406,7 +3406,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>134.6028150731275</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>197.2737972923793</v>
@@ -3634,7 +3634,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
-        <v>72.68247130380102</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
         <v>64.51066719152016</v>
@@ -3643,7 +3643,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>69.86273944538755</v>
+        <v>139.8684047489176</v>
       </c>
       <c r="Y39" t="n">
         <v>49.39139276613435</v>
@@ -3744,7 +3744,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>54.36328960686865</v>
+        <v>62.20948099228315</v>
       </c>
       <c r="F41" t="n">
         <v>54.88962870801186</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T41" t="n">
         <v>236.6755817285639</v>
@@ -3868,22 +3868,22 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>118.0355277429563</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U42" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V42" t="n">
         <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3972,28 +3972,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>131.9993129555745</v>
+        <v>132.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>99.47457824299391</v>
+        <v>100.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>60.33915573984979</v>
+        <v>61.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>54.36328960686865</v>
+        <v>55.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>54.88962870801186</v>
+        <v>55.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>53.75737228701621</v>
+        <v>54.75737228701621</v>
       </c>
       <c r="H44" t="n">
-        <v>58.00965870352741</v>
+        <v>59.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>144.8481678023229</v>
+        <v>145.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>236.6755817285639</v>
+        <v>237.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>299.2212965486107</v>
+        <v>300.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>279.8510241668239</v>
+        <v>280.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>288.3734759809475</v>
+        <v>289.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>242.2818334606677</v>
+        <v>243.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>161.3174326828064</v>
+        <v>156.1636240682211</v>
       </c>
     </row>
     <row r="45">
@@ -4051,16 +4051,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>35.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>11.09991244551929</v>
+        <v>12.09991244551929</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>53.6777625254426</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,28 +4099,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>198.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>117.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>50.21035976018675</v>
+        <v>51.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>65.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>82.37314290982852</v>
+        <v>83.37314290982852</v>
       </c>
       <c r="X45" t="n">
-        <v>139.8684047489175</v>
+        <v>70.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>49.39139276613435</v>
+        <v>50.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4160,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>73.54762815777917</v>
+        <v>74.54762815777917</v>
       </c>
       <c r="M46" t="n">
-        <v>170.6316114025499</v>
+        <v>171.6316114025499</v>
       </c>
       <c r="N46" t="n">
-        <v>221.1850752716849</v>
+        <v>222.1850752716849</v>
       </c>
       <c r="O46" t="n">
-        <v>290.445564079015</v>
+        <v>288.7711186273551</v>
       </c>
       <c r="P46" t="n">
-        <v>337.4478973282775</v>
+        <v>338.4478973282775</v>
       </c>
       <c r="Q46" t="n">
-        <v>375.839266425598</v>
+        <v>376.839266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>376.6021279811511</v>
+        <v>377.6021279811511</v>
       </c>
       <c r="S46" t="n">
-        <v>12.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.4501851396645</v>
+        <v>111.8901851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>62.47586368209485</v>
+        <v>61.91586368209486</v>
       </c>
       <c r="D2" t="n">
-        <v>52.03227202568092</v>
+        <v>51.47227202568093</v>
       </c>
       <c r="E2" t="n">
-        <v>47.62490878641967</v>
+        <v>47.06490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68588988943799</v>
+        <v>42.125889889438</v>
       </c>
       <c r="G2" t="n">
-        <v>38.89056434699738</v>
+        <v>38.33056434699738</v>
       </c>
       <c r="H2" t="n">
-        <v>30.8</v>
+        <v>30.24</v>
       </c>
       <c r="I2" t="n">
-        <v>30.8</v>
+        <v>30.24</v>
       </c>
       <c r="J2" t="n">
-        <v>396.55</v>
+        <v>30.24</v>
       </c>
       <c r="K2" t="n">
-        <v>396.55</v>
+        <v>30.24</v>
       </c>
       <c r="L2" t="n">
-        <v>396.55</v>
+        <v>30.24</v>
       </c>
       <c r="M2" t="n">
-        <v>396.55</v>
+        <v>404.46</v>
       </c>
       <c r="N2" t="n">
-        <v>396.55</v>
+        <v>778.6799999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>777.6999999999999</v>
+        <v>1152.9</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1152.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>1540</v>
+        <v>1512</v>
       </c>
       <c r="R2" t="n">
-        <v>1511.00384708544</v>
+        <v>1512</v>
       </c>
       <c r="S2" t="n">
-        <v>1415.197616982083</v>
+        <v>1414.637616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1226.636423316867</v>
+        <v>1226.076423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>974.8977399344323</v>
+        <v>974.3377399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>742.7249882507717</v>
+        <v>742.1649882507718</v>
       </c>
       <c r="W2" t="n">
-        <v>501.9436993811278</v>
+        <v>501.3836993811278</v>
       </c>
       <c r="X2" t="n">
-        <v>307.7196251784331</v>
+        <v>307.1596251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.2777739836791</v>
+        <v>194.7177739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>719.9408141797186</v>
+        <v>1048.129558715245</v>
       </c>
       <c r="C3" t="n">
-        <v>719.9408141797186</v>
+        <v>1048.129558715245</v>
       </c>
       <c r="D3" t="n">
-        <v>719.9408141797186</v>
+        <v>1048.129558715245</v>
       </c>
       <c r="E3" t="n">
-        <v>719.9408141797186</v>
+        <v>1048.129558715245</v>
       </c>
       <c r="F3" t="n">
-        <v>384.5675796314646</v>
+        <v>911.4104817302218</v>
       </c>
       <c r="G3" t="n">
-        <v>384.5675796314646</v>
+        <v>911.4104817302218</v>
       </c>
       <c r="H3" t="n">
-        <v>384.5675796314646</v>
+        <v>575.8871613398975</v>
       </c>
       <c r="I3" t="n">
-        <v>384.5675796314646</v>
+        <v>356.5675796314646</v>
       </c>
       <c r="J3" t="n">
-        <v>508.5240998067635</v>
+        <v>480.5240998067635</v>
       </c>
       <c r="K3" t="n">
-        <v>697.7169159011469</v>
+        <v>669.7169159011469</v>
       </c>
       <c r="L3" t="n">
-        <v>969.0673774963469</v>
+        <v>941.0673774963469</v>
       </c>
       <c r="M3" t="n">
-        <v>1055.147919239206</v>
+        <v>1027.147919239206</v>
       </c>
       <c r="N3" t="n">
-        <v>1188.428203846775</v>
+        <v>1160.428203846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1427.470655530493</v>
+        <v>1399.470655530493</v>
       </c>
       <c r="P3" t="n">
-        <v>1540</v>
+        <v>1512</v>
       </c>
       <c r="Q3" t="n">
-        <v>1365.172459504566</v>
+        <v>1337.172459504566</v>
       </c>
       <c r="R3" t="n">
-        <v>1216.411048098122</v>
+        <v>1188.411048098122</v>
       </c>
       <c r="S3" t="n">
-        <v>1149.174684497505</v>
+        <v>1121.174684497505</v>
       </c>
       <c r="T3" t="n">
-        <v>1143.76280043941</v>
+        <v>1115.76280043941</v>
       </c>
       <c r="U3" t="n">
-        <v>1143.550315833161</v>
+        <v>1115.550315833161</v>
       </c>
       <c r="V3" t="n">
-        <v>1128.893076245767</v>
+        <v>1100.893076245767</v>
       </c>
       <c r="W3" t="n">
-        <v>740.0041873568778</v>
+        <v>1068.192931892404</v>
       </c>
       <c r="X3" t="n">
-        <v>719.9408141797186</v>
+        <v>1048.129558715245</v>
       </c>
       <c r="Y3" t="n">
-        <v>719.9408141797186</v>
+        <v>1048.129558715245</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>871.2301421292345</v>
+        <v>899.5459187472545</v>
       </c>
       <c r="C4" t="n">
-        <v>997.2321479476703</v>
+        <v>1025.54792456569</v>
       </c>
       <c r="D4" t="n">
-        <v>997.2321479476703</v>
+        <v>1138.86706869069</v>
       </c>
       <c r="E4" t="n">
-        <v>1115.061052159083</v>
+        <v>1138.86706869069</v>
       </c>
       <c r="F4" t="n">
-        <v>1115.061052159083</v>
+        <v>1248.229000176246</v>
       </c>
       <c r="G4" t="n">
-        <v>1115.061052159083</v>
+        <v>1401.635566063132</v>
       </c>
       <c r="H4" t="n">
-        <v>1284.577637318481</v>
+        <v>1401.635566063132</v>
       </c>
       <c r="I4" t="n">
-        <v>1429.635566063132</v>
+        <v>1401.635566063132</v>
       </c>
       <c r="J4" t="n">
-        <v>1429.635566063132</v>
+        <v>1401.635566063132</v>
       </c>
       <c r="K4" t="n">
-        <v>1540</v>
+        <v>1512</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.821760089168</v>
+        <v>1512</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1390.149887472172</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1217.235670026025</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>974.3613628755053</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>684.0099514328008</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>360.1411393749001</v>
       </c>
       <c r="R4" t="n">
-        <v>30.8</v>
+        <v>30.24</v>
       </c>
       <c r="S4" t="n">
-        <v>30.8</v>
+        <v>30.24</v>
       </c>
       <c r="T4" t="n">
-        <v>30.8</v>
+        <v>218.3156791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>277.3511926382866</v>
+        <v>464.8668717970915</v>
       </c>
       <c r="V4" t="n">
-        <v>476.1725855242326</v>
+        <v>464.8668717970915</v>
       </c>
       <c r="W4" t="n">
-        <v>648.0635037839101</v>
+        <v>636.757790056769</v>
       </c>
       <c r="X4" t="n">
-        <v>648.0635037839101</v>
+        <v>787.7885810809624</v>
       </c>
       <c r="Y4" t="n">
-        <v>759.4728044629423</v>
+        <v>787.7885810809624</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.4463380542246</v>
+        <v>112.5301851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>91.47201659665494</v>
+        <v>62.55586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>52.03227202568092</v>
+        <v>52.11227202568092</v>
       </c>
       <c r="E5" t="n">
-        <v>47.62490878641967</v>
+        <v>47.70490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>42.76588988943799</v>
       </c>
       <c r="G5" t="n">
-        <v>38.89056434699738</v>
+        <v>38.97056434699738</v>
       </c>
       <c r="H5" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="I5" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J5" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="K5" t="n">
-        <v>411.9499999999999</v>
+        <v>413.0199999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>411.9499999999999</v>
+        <v>413.0199999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>793.0999999999999</v>
+        <v>795.16</v>
       </c>
       <c r="N5" t="n">
-        <v>1174.25</v>
+        <v>1177.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="P5" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="Q5" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="R5" t="n">
-        <v>1540</v>
+        <v>1511.08384708544</v>
       </c>
       <c r="S5" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.277616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.716423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.9777399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.8049882507718</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>502.0236993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7996251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.2739268982392</v>
+        <v>195.3577739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.8</v>
+        <v>359.9098342171994</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>359.9098342171994</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>359.9098342171994</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>359.9098342171994</v>
       </c>
       <c r="F6" t="n">
-        <v>30.8</v>
+        <v>359.9098342171994</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="H6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="I6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J6" t="n">
-        <v>154.756520175299</v>
+        <v>154.8365201752989</v>
       </c>
       <c r="K6" t="n">
-        <v>343.9493362696824</v>
+        <v>344.0293362696823</v>
       </c>
       <c r="L6" t="n">
-        <v>615.2997978648825</v>
+        <v>615.3797978648824</v>
       </c>
       <c r="M6" t="n">
-        <v>701.3803396077418</v>
+        <v>701.4603396077417</v>
       </c>
       <c r="N6" t="n">
-        <v>834.6606242153101</v>
+        <v>834.74062421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1073.703075899029</v>
+        <v>1073.783075899029</v>
       </c>
       <c r="P6" t="n">
-        <v>1186.232420368536</v>
+        <v>1186.312420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1186.232420368536</v>
+        <v>1186.312420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1037.471008962092</v>
+        <v>1037.551008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>876.2110195019425</v>
+        <v>970.3146453614744</v>
       </c>
       <c r="T6" t="n">
-        <v>487.3221306130535</v>
+        <v>802.7848262529599</v>
       </c>
       <c r="U6" t="n">
-        <v>487.1096460068043</v>
+        <v>802.5723416467106</v>
       </c>
       <c r="V6" t="n">
-        <v>472.4524064194102</v>
+        <v>412.6733517477206</v>
       </c>
       <c r="W6" t="n">
-        <v>439.752262066048</v>
+        <v>379.9732073943585</v>
       </c>
       <c r="X6" t="n">
-        <v>419.6888888888889</v>
+        <v>359.9098342171994</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.8</v>
+        <v>359.9098342171994</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>824.7209153808315</v>
+        <v>513.3496488119156</v>
       </c>
       <c r="C7" t="n">
-        <v>950.7229211992673</v>
+        <v>639.3516546303514</v>
       </c>
       <c r="D7" t="n">
-        <v>950.7229211992673</v>
+        <v>752.6707987553515</v>
       </c>
       <c r="E7" t="n">
-        <v>1068.55182541068</v>
+        <v>870.4997029667645</v>
       </c>
       <c r="F7" t="n">
-        <v>1068.55182541068</v>
+        <v>994.8606755587</v>
       </c>
       <c r="G7" t="n">
-        <v>1068.55182541068</v>
+        <v>1148.267241445585</v>
       </c>
       <c r="H7" t="n">
-        <v>1068.55182541068</v>
+        <v>1180.603502424373</v>
       </c>
       <c r="I7" t="n">
-        <v>1068.55182541068</v>
+        <v>1180.603502424373</v>
       </c>
       <c r="J7" t="n">
-        <v>1429.635566063132</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="K7" t="n">
-        <v>1540</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="L7" t="n">
-        <v>1517.821760089168</v>
+        <v>1517.901760089168</v>
       </c>
       <c r="M7" t="n">
-        <v>1395.97164756134</v>
+        <v>1396.05164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1223.057430115194</v>
+        <v>1223.137430115194</v>
       </c>
       <c r="O7" t="n">
-        <v>980.1831229646734</v>
+        <v>980.2631229646734</v>
       </c>
       <c r="P7" t="n">
-        <v>689.8317115219688</v>
+        <v>689.9117115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>360.7011393749001</v>
+        <v>360.7811393749001</v>
       </c>
       <c r="R7" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="S7" t="n">
-        <v>68.05025509417312</v>
+        <v>30.88</v>
       </c>
       <c r="T7" t="n">
-        <v>256.125934252978</v>
+        <v>30.88</v>
       </c>
       <c r="U7" t="n">
-        <v>502.6771268912646</v>
+        <v>30.88</v>
       </c>
       <c r="V7" t="n">
-        <v>561.9327866903458</v>
+        <v>229.7013928859459</v>
       </c>
       <c r="W7" t="n">
-        <v>561.9327866903458</v>
+        <v>401.5923111456234</v>
       </c>
       <c r="X7" t="n">
-        <v>712.9635777145393</v>
+        <v>401.5923111456234</v>
       </c>
       <c r="Y7" t="n">
-        <v>712.9635777145393</v>
+        <v>401.5923111456234</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.4463380542246</v>
+        <v>145.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>62.47586368209485</v>
+        <v>95.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>52.03227202568092</v>
+        <v>85.02842494024101</v>
       </c>
       <c r="E8" t="n">
-        <v>47.62490878641967</v>
+        <v>80.62106170097975</v>
       </c>
       <c r="F8" t="n">
-        <v>42.68588988943799</v>
+        <v>75.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>71.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>63.79615291456007</v>
       </c>
       <c r="I8" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J8" t="n">
-        <v>411.95</v>
+        <v>413.02</v>
       </c>
       <c r="K8" t="n">
-        <v>411.95</v>
+        <v>413.02</v>
       </c>
       <c r="L8" t="n">
-        <v>777.6999999999999</v>
+        <v>779.7200000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1158.85</v>
+        <v>1161.86</v>
       </c>
       <c r="N8" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="O8" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="P8" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="Q8" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="R8" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="S8" t="n">
-        <v>1444.193769896644</v>
+        <v>1448.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1255.632576231427</v>
+        <v>1259.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>1003.893892848992</v>
+        <v>1007.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>771.7211411653319</v>
+        <v>775.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>530.9398522956878</v>
+        <v>534.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>336.7157780929932</v>
+        <v>340.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>224.2739268982392</v>
+        <v>228.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.8</v>
+        <v>366.4033203903244</v>
       </c>
       <c r="C9" t="n">
-        <v>30.8</v>
+        <v>366.4033203903244</v>
       </c>
       <c r="D9" t="n">
-        <v>30.8</v>
+        <v>366.4033203903244</v>
       </c>
       <c r="E9" t="n">
-        <v>30.8</v>
+        <v>366.4033203903244</v>
       </c>
       <c r="F9" t="n">
-        <v>30.8</v>
+        <v>366.4033203903244</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>366.4033203903244</v>
       </c>
       <c r="H9" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="I9" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J9" t="n">
-        <v>154.756520175299</v>
+        <v>154.8365201752989</v>
       </c>
       <c r="K9" t="n">
-        <v>343.9493362696824</v>
+        <v>344.0293362696823</v>
       </c>
       <c r="L9" t="n">
-        <v>615.2997978648825</v>
+        <v>615.3797978648824</v>
       </c>
       <c r="M9" t="n">
-        <v>701.3803396077418</v>
+        <v>701.4603396077417</v>
       </c>
       <c r="N9" t="n">
-        <v>834.6606242153101</v>
+        <v>834.74062421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1073.703075899029</v>
+        <v>1073.783075899029</v>
       </c>
       <c r="P9" t="n">
-        <v>1186.232420368536</v>
+        <v>1186.312420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1186.232420368536</v>
+        <v>1186.312420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1037.471008962092</v>
+        <v>1037.551008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>846.9022907954841</v>
+        <v>647.652019063102</v>
       </c>
       <c r="T9" t="n">
-        <v>841.4904067373893</v>
+        <v>434.036562114489</v>
       </c>
       <c r="U9" t="n">
-        <v>841.27792213114</v>
+        <v>433.8240775082397</v>
       </c>
       <c r="V9" t="n">
-        <v>452.3890332422511</v>
+        <v>419.1668379208456</v>
       </c>
       <c r="W9" t="n">
-        <v>419.6888888888889</v>
+        <v>386.4666935674835</v>
       </c>
       <c r="X9" t="n">
-        <v>30.8</v>
+        <v>366.4033203903244</v>
       </c>
       <c r="Y9" t="n">
-        <v>30.8</v>
+        <v>366.4033203903244</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>403.7121810287699</v>
+        <v>560.7314115769964</v>
       </c>
       <c r="C10" t="n">
-        <v>403.7121810287699</v>
+        <v>560.7314115769964</v>
       </c>
       <c r="D10" t="n">
-        <v>517.03132515377</v>
+        <v>560.7314115769964</v>
       </c>
       <c r="E10" t="n">
-        <v>634.860229365183</v>
+        <v>560.7314115769964</v>
       </c>
       <c r="F10" t="n">
-        <v>634.860229365183</v>
+        <v>685.0923841689319</v>
       </c>
       <c r="G10" t="n">
-        <v>788.2667952520683</v>
+        <v>685.0923841689319</v>
       </c>
       <c r="H10" t="n">
-        <v>957.7833804114658</v>
+        <v>854.6089693283294</v>
       </c>
       <c r="I10" t="n">
-        <v>1178.916259347549</v>
+        <v>1075.741848264412</v>
       </c>
       <c r="J10" t="n">
-        <v>1540</v>
+        <v>1436.825588916864</v>
       </c>
       <c r="K10" t="n">
-        <v>1540</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.821760089168</v>
+        <v>1517.901760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1395.97164756134</v>
+        <v>1396.05164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.057430115194</v>
+        <v>1223.137430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>980.1831229646734</v>
+        <v>980.2631229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>689.8317115219688</v>
+        <v>689.9117115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>360.7011393749001</v>
+        <v>360.7811393749001</v>
       </c>
       <c r="R10" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="S10" t="n">
-        <v>68.05025509417312</v>
+        <v>30.88</v>
       </c>
       <c r="T10" t="n">
-        <v>252.6813900045764</v>
+        <v>30.88</v>
       </c>
       <c r="U10" t="n">
-        <v>252.6813900045764</v>
+        <v>277.4311926382866</v>
       </c>
       <c r="V10" t="n">
-        <v>252.6813900045764</v>
+        <v>277.4311926382866</v>
       </c>
       <c r="W10" t="n">
-        <v>252.6813900045764</v>
+        <v>449.3221108979641</v>
       </c>
       <c r="X10" t="n">
-        <v>403.7121810287699</v>
+        <v>449.3221108979641</v>
       </c>
       <c r="Y10" t="n">
-        <v>403.7121810287699</v>
+        <v>560.7314115769964</v>
       </c>
     </row>
     <row r="11">
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C11" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D11" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E11" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F11" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G11" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H11" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I11" t="n">
         <v>81.36</v>
@@ -5035,19 +5035,19 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>472.6691130376557</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>690.7012485145707</v>
+        <v>2089.404973955146</v>
       </c>
       <c r="M11" t="n">
-        <v>1201.550077243506</v>
+        <v>2600.253802684082</v>
       </c>
       <c r="N11" t="n">
-        <v>1814.770397018269</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="O11" t="n">
-        <v>2767.812941040225</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="P11" t="n">
         <v>3629.400904947332</v>
@@ -5077,7 +5077,7 @@
         <v>1777.969718670473</v>
       </c>
       <c r="Y11" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="12">
@@ -5108,28 +5108,28 @@
         <v>81.36</v>
       </c>
       <c r="I12" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J12" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K12" t="n">
-        <v>643.9799167834981</v>
+        <v>695.3814443439232</v>
       </c>
       <c r="L12" t="n">
-        <v>1138.080378378698</v>
+        <v>1189.481905939123</v>
       </c>
       <c r="M12" t="n">
-        <v>1446.910920121557</v>
+        <v>1498.312447681983</v>
       </c>
       <c r="N12" t="n">
-        <v>1802.941204729126</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O12" t="n">
-        <v>2264.733656412845</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P12" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q12" t="n">
         <v>2651.414528442776</v>
@@ -5166,49 +5166,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="C13" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="D13" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="E13" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="F13" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="G13" t="n">
-        <v>173.4252518747145</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="H13" t="n">
-        <v>173.4252518747145</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="I13" t="n">
-        <v>221.3081308107974</v>
+        <v>242.9411436191204</v>
       </c>
       <c r="J13" t="n">
-        <v>409.1418714632487</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="K13" t="n">
-        <v>409.1418714632487</v>
+        <v>430.7748842715717</v>
       </c>
       <c r="L13" t="n">
-        <v>409.1418714632487</v>
+        <v>230.2217245162392</v>
       </c>
       <c r="M13" t="n">
-        <v>110.5240821677438</v>
+        <v>81.36</v>
       </c>
       <c r="N13" t="n">
-        <v>110.5240821677438</v>
+        <v>81.36</v>
       </c>
       <c r="O13" t="n">
-        <v>110.5240821677438</v>
+        <v>81.36</v>
       </c>
       <c r="P13" t="n">
-        <v>110.5240821677438</v>
+        <v>81.36</v>
       </c>
       <c r="Q13" t="n">
         <v>81.36</v>
@@ -5229,13 +5229,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X13" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y13" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="14">
@@ -5263,13 +5263,13 @@
         <v>271.7669204653003</v>
       </c>
       <c r="H14" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I14" t="n">
         <v>81.36</v>
       </c>
       <c r="J14" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K14" t="n">
         <v>690.7012485145707</v>
@@ -5345,25 +5345,25 @@
         <v>81.36</v>
       </c>
       <c r="I15" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>428.066520175299</v>
+        <v>283.4386282495398</v>
       </c>
       <c r="K15" t="n">
-        <v>840.0093362696824</v>
+        <v>695.3814443439232</v>
       </c>
       <c r="L15" t="n">
-        <v>1334.109797864882</v>
+        <v>1189.481905939123</v>
       </c>
       <c r="M15" t="n">
-        <v>1642.940339607742</v>
+        <v>1498.312447681983</v>
       </c>
       <c r="N15" t="n">
-        <v>1998.97062421531</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O15" t="n">
-        <v>2460.763075899029</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P15" t="n">
         <v>2651.414528442776</v>
@@ -5421,37 +5421,37 @@
         <v>195.0582646830375</v>
       </c>
       <c r="H16" t="n">
-        <v>195.0582646830375</v>
+        <v>191.2490463985742</v>
       </c>
       <c r="I16" t="n">
-        <v>242.9411436191204</v>
+        <v>239.1319253346571</v>
       </c>
       <c r="J16" t="n">
-        <v>430.7748842715717</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="K16" t="n">
-        <v>430.7748842715717</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="L16" t="n">
-        <v>430.7748842715717</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="M16" t="n">
-        <v>430.7748842715717</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="N16" t="n">
-        <v>430.7748842715717</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="O16" t="n">
-        <v>430.7748842715717</v>
+        <v>426.9656659871084</v>
       </c>
       <c r="P16" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="R16" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="S16" t="n">
         <v>81.36</v>
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C17" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D17" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E17" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F17" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G17" t="n">
         <v>266.2182411146742</v>
@@ -5506,25 +5506,25 @@
         <v>81.36</v>
       </c>
       <c r="J17" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>791.0663663478683</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1698.095860917491</v>
+        <v>2089.404973955146</v>
       </c>
       <c r="M17" t="n">
-        <v>2208.944689646426</v>
+        <v>2600.253802684082</v>
       </c>
       <c r="N17" t="n">
-        <v>2822.165009421189</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="O17" t="n">
-        <v>3775.207553443145</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>3775.207553443145</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>4068</v>
@@ -5533,25 +5533,25 @@
         <v>4041.860001183541</v>
       </c>
       <c r="S17" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T17" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U17" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V17" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W17" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X17" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y17" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="18">
@@ -5582,19 +5582,19 @@
         <v>81.36</v>
       </c>
       <c r="I18" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J18" t="n">
-        <v>428.066520175299</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K18" t="n">
-        <v>840.0093362696824</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L18" t="n">
-        <v>1334.109797864882</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M18" t="n">
-        <v>1642.940339607742</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N18" t="n">
         <v>1802.941204729126</v>
@@ -5640,55 +5640,55 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="C19" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="D19" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="E19" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="F19" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="G19" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="H19" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
       <c r="I19" t="n">
-        <v>241.5544670143631</v>
+        <v>179.8448276095624</v>
       </c>
       <c r="J19" t="n">
-        <v>429.3882076668144</v>
+        <v>367.6785682620138</v>
       </c>
       <c r="K19" t="n">
-        <v>429.3882076668144</v>
+        <v>367.6785682620138</v>
       </c>
       <c r="L19" t="n">
-        <v>429.3882076668144</v>
+        <v>167.1254085066813</v>
       </c>
       <c r="M19" t="n">
-        <v>429.3882076668144</v>
+        <v>167.1254085066813</v>
       </c>
       <c r="N19" t="n">
-        <v>429.3882076668144</v>
+        <v>167.1254085066813</v>
       </c>
       <c r="O19" t="n">
-        <v>220.1210906089449</v>
+        <v>167.1254085066813</v>
       </c>
       <c r="P19" t="n">
-        <v>220.1210906089449</v>
+        <v>167.1254085066813</v>
       </c>
       <c r="Q19" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="R19" t="n">
-        <v>220.1210906089449</v>
+        <v>81.36</v>
       </c>
       <c r="S19" t="n">
         <v>81.36</v>
@@ -5703,13 +5703,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X19" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y19" t="n">
-        <v>193.6715880782802</v>
+        <v>131.9619486734795</v>
       </c>
     </row>
     <row r="20">
@@ -5743,40 +5743,40 @@
         <v>81.36</v>
       </c>
       <c r="J20" t="n">
-        <v>374.1524465568547</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1083.858812904723</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1990.888307474345</v>
+        <v>1379.698607607278</v>
       </c>
       <c r="M20" t="n">
-        <v>2501.73713620328</v>
+        <v>1890.547436336213</v>
       </c>
       <c r="N20" t="n">
-        <v>3114.957455978044</v>
+        <v>1890.547436336213</v>
       </c>
       <c r="O20" t="n">
-        <v>4068</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P20" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>4068</v>
       </c>
       <c r="R20" t="n">
-        <v>4041.860001183541</v>
+        <v>4036.311321832915</v>
       </c>
       <c r="S20" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T20" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U20" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V20" t="n">
         <v>2560.961755927539</v>
@@ -5819,16 +5819,16 @@
         <v>81.36</v>
       </c>
       <c r="I21" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J21" t="n">
-        <v>428.066520175299</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>643.9799167834981</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L21" t="n">
-        <v>1138.080378378698</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M21" t="n">
         <v>1446.910920121557</v>
@@ -5877,49 +5877,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="I22" t="n">
-        <v>242.9411436191204</v>
+        <v>241.5544670143631</v>
       </c>
       <c r="J22" t="n">
-        <v>430.7748842715717</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="K22" t="n">
-        <v>430.7748842715717</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="L22" t="n">
-        <v>430.7748842715717</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="M22" t="n">
-        <v>430.7748842715717</v>
+        <v>130.7704183713095</v>
       </c>
       <c r="N22" t="n">
-        <v>430.7748842715717</v>
+        <v>130.7704183713095</v>
       </c>
       <c r="O22" t="n">
-        <v>430.7748842715717</v>
+        <v>130.7704183713095</v>
       </c>
       <c r="P22" t="n">
-        <v>81.36</v>
+        <v>130.7704183713095</v>
       </c>
       <c r="Q22" t="n">
         <v>81.36</v>
@@ -5940,13 +5940,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="23">
@@ -5992,10 +5992,10 @@
         <v>1890.547436336213</v>
       </c>
       <c r="N23" t="n">
-        <v>2503.767756110976</v>
+        <v>1890.547436336213</v>
       </c>
       <c r="O23" t="n">
-        <v>3456.810300132933</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P23" t="n">
         <v>3629.400904947332</v>
@@ -6004,22 +6004,22 @@
         <v>4068</v>
       </c>
       <c r="R23" t="n">
-        <v>4041.860001183541</v>
+        <v>4036.311321832915</v>
       </c>
       <c r="S23" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T23" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U23" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W23" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X23" t="n">
         <v>1772.421039319847</v>
@@ -6056,22 +6056,22 @@
         <v>81.36</v>
       </c>
       <c r="I24" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J24" t="n">
-        <v>428.066520175299</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>840.0093362696824</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L24" t="n">
-        <v>1334.109797864882</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M24" t="n">
-        <v>1446.910920121557</v>
+        <v>1650.735217575307</v>
       </c>
       <c r="N24" t="n">
-        <v>1802.941204729126</v>
+        <v>2006.765502182875</v>
       </c>
       <c r="O24" t="n">
         <v>2264.733656412845</v>
@@ -6114,52 +6114,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="C25" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="D25" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="E25" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="F25" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="G25" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
       <c r="H25" t="n">
-        <v>193.6715880782802</v>
+        <v>126.766053784259</v>
       </c>
       <c r="I25" t="n">
-        <v>241.5544670143631</v>
+        <v>174.6489327203419</v>
       </c>
       <c r="J25" t="n">
-        <v>429.3882076668144</v>
+        <v>362.4826733727932</v>
       </c>
       <c r="K25" t="n">
-        <v>429.3882076668144</v>
+        <v>362.4826733727932</v>
       </c>
       <c r="L25" t="n">
-        <v>429.3882076668144</v>
+        <v>362.4826733727932</v>
       </c>
       <c r="M25" t="n">
-        <v>429.3882076668144</v>
+        <v>362.4826733727932</v>
       </c>
       <c r="N25" t="n">
-        <v>429.3882076668144</v>
+        <v>81.36</v>
       </c>
       <c r="O25" t="n">
-        <v>429.3882076668144</v>
+        <v>81.36</v>
       </c>
       <c r="P25" t="n">
-        <v>429.3882076668144</v>
+        <v>81.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>429.3882076668144</v>
+        <v>81.36</v>
       </c>
       <c r="R25" t="n">
         <v>81.36</v>
@@ -6183,7 +6183,7 @@
         <v>193.6715880782802</v>
       </c>
       <c r="Y25" t="n">
-        <v>193.6715880782802</v>
+        <v>130.5752720687223</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1229.164925096351</v>
+        <v>1252.074016005442</v>
       </c>
       <c r="C26" t="n">
-        <v>996.8742475204788</v>
+        <v>1024.321916770095</v>
       </c>
       <c r="D26" t="n">
-        <v>809.6629790963881</v>
+        <v>836.100547335903</v>
       </c>
       <c r="E26" t="n">
-        <v>628.48793908945</v>
+        <v>653.9154063188639</v>
       </c>
       <c r="F26" t="n">
-        <v>446.7812434247916</v>
+        <v>471.1986096441045</v>
       </c>
       <c r="G26" t="n">
-        <v>266.2182411146742</v>
+        <v>267.8683421247752</v>
       </c>
       <c r="H26" t="n">
-        <v>81.36</v>
+        <v>82</v>
       </c>
       <c r="I26" t="n">
-        <v>81.36</v>
+        <v>82</v>
       </c>
       <c r="J26" t="n">
-        <v>81.36</v>
+        <v>473.3091130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>791.0663663478683</v>
+        <v>1183.015479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1129.300343567238</v>
+        <v>2090.044973955146</v>
       </c>
       <c r="M26" t="n">
-        <v>1640.149172296173</v>
+        <v>2600.893802684081</v>
       </c>
       <c r="N26" t="n">
-        <v>2253.369492070936</v>
+        <v>3214.114122458845</v>
       </c>
       <c r="O26" t="n">
-        <v>3206.412036092893</v>
+        <v>3214.114122458845</v>
       </c>
       <c r="P26" t="n">
-        <v>4068</v>
+        <v>3661.400904947332</v>
       </c>
       <c r="Q26" t="n">
-        <v>4068</v>
+        <v>4100</v>
       </c>
       <c r="R26" t="n">
-        <v>4041.860001183541</v>
+        <v>4072.84990017344</v>
       </c>
       <c r="S26" t="n">
-        <v>3769.286094312508</v>
+        <v>3799.265892292306</v>
       </c>
       <c r="T26" t="n">
-        <v>3403.957223879615</v>
+        <v>3432.926920849312</v>
       </c>
       <c r="U26" t="n">
-        <v>2975.450863729503</v>
+        <v>3003.410459689099</v>
       </c>
       <c r="V26" t="n">
-        <v>2566.510435278165</v>
+        <v>2593.459930227661</v>
       </c>
       <c r="W26" t="n">
-        <v>2148.961469640845</v>
+        <v>2174.900863580239</v>
       </c>
       <c r="X26" t="n">
-        <v>1777.969718670473</v>
+        <v>1802.899011599766</v>
       </c>
       <c r="Y26" t="n">
-        <v>1488.760190708043</v>
+        <v>1512.679382627235</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>787.6767292570302</v>
+        <v>794.3773353176364</v>
       </c>
       <c r="C27" t="n">
-        <v>650.2020702211521</v>
+        <v>655.8925752716573</v>
       </c>
       <c r="D27" t="n">
-        <v>526.022588506301</v>
+        <v>530.7029925467051</v>
       </c>
       <c r="E27" t="n">
-        <v>407.1618842417428</v>
+        <v>410.8321872720459</v>
       </c>
       <c r="F27" t="n">
-        <v>291.3677000620692</v>
+        <v>294.0279020822712</v>
       </c>
       <c r="G27" t="n">
-        <v>189.6105931175971</v>
+        <v>191.2606941276981</v>
       </c>
       <c r="H27" t="n">
-        <v>81.36</v>
+        <v>82</v>
       </c>
       <c r="I27" t="n">
-        <v>89.15487796756496</v>
+        <v>82</v>
       </c>
       <c r="J27" t="n">
-        <v>435.8613981428639</v>
+        <v>427.716520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>847.8042142372474</v>
+        <v>665.7114319350128</v>
       </c>
       <c r="L27" t="n">
-        <v>1138.080378378698</v>
+        <v>1158.821893530213</v>
       </c>
       <c r="M27" t="n">
-        <v>1446.910920121557</v>
+        <v>1466.662435273072</v>
       </c>
       <c r="N27" t="n">
-        <v>1802.941204729126</v>
+        <v>1821.70271988064</v>
       </c>
       <c r="O27" t="n">
-        <v>2264.733656412845</v>
+        <v>2282.505171564359</v>
       </c>
       <c r="P27" t="n">
-        <v>2600.013000882351</v>
+        <v>2616.794516033866</v>
       </c>
       <c r="Q27" t="n">
-        <v>2651.414528442776</v>
+        <v>2667.206043594291</v>
       </c>
       <c r="R27" t="n">
-        <v>2325.885440268656</v>
+        <v>2340.66685441007</v>
       </c>
       <c r="S27" t="n">
-        <v>2081.881399900361</v>
+        <v>2095.652713031674</v>
       </c>
       <c r="T27" t="n">
-        <v>1899.70183907459</v>
+        <v>1912.463051195802</v>
       </c>
       <c r="U27" t="n">
-        <v>1722.721677700664</v>
+        <v>1734.472788811775</v>
       </c>
       <c r="V27" t="n">
-        <v>1531.296761345593</v>
+        <v>1542.037771446603</v>
       </c>
       <c r="W27" t="n">
-        <v>1321.828940224554</v>
+        <v>1331.559849315463</v>
       </c>
       <c r="X27" t="n">
-        <v>1124.997890279718</v>
+        <v>1133.718698360526</v>
       </c>
       <c r="Y27" t="n">
-        <v>948.8449682937237</v>
+        <v>956.555675364431</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>193.6715880782802</v>
+        <v>198.1945361668876</v>
       </c>
       <c r="C28" t="n">
-        <v>193.6715880782802</v>
+        <v>148.9771153102769</v>
       </c>
       <c r="D28" t="n">
-        <v>193.6715880782802</v>
+        <v>86.81931929456427</v>
       </c>
       <c r="E28" t="n">
-        <v>193.6715880782802</v>
+        <v>86.81931929456427</v>
       </c>
       <c r="F28" t="n">
-        <v>193.6715880782802</v>
+        <v>86.81931929456427</v>
       </c>
       <c r="G28" t="n">
-        <v>193.6715880782802</v>
+        <v>86.81931929456427</v>
       </c>
       <c r="H28" t="n">
-        <v>189.862369793817</v>
+        <v>82</v>
       </c>
       <c r="I28" t="n">
-        <v>237.7452487298999</v>
+        <v>128.8928789360829</v>
       </c>
       <c r="J28" t="n">
-        <v>425.5789893823512</v>
+        <v>315.7366195885343</v>
       </c>
       <c r="K28" t="n">
-        <v>425.5789893823512</v>
+        <v>315.7366195885343</v>
       </c>
       <c r="L28" t="n">
-        <v>425.5789893823512</v>
+        <v>315.7366195885343</v>
       </c>
       <c r="M28" t="n">
-        <v>425.5789893823512</v>
+        <v>315.7366195885343</v>
       </c>
       <c r="N28" t="n">
-        <v>425.5789893823512</v>
+        <v>315.7366195885343</v>
       </c>
       <c r="O28" t="n">
-        <v>425.5789893823512</v>
+        <v>315.7366195885343</v>
       </c>
       <c r="P28" t="n">
-        <v>425.5789893823512</v>
+        <v>315.7366195885343</v>
       </c>
       <c r="Q28" t="n">
-        <v>81.36</v>
+        <v>315.7366195885343</v>
       </c>
       <c r="R28" t="n">
-        <v>81.36</v>
+        <v>87.46627148385016</v>
       </c>
       <c r="S28" t="n">
-        <v>81.36</v>
+        <v>87.46627148385016</v>
       </c>
       <c r="T28" t="n">
-        <v>96.18567915880486</v>
+        <v>101.301950642655</v>
       </c>
       <c r="U28" t="n">
-        <v>169.4868717970915</v>
+        <v>173.6131432809417</v>
       </c>
       <c r="V28" t="n">
-        <v>195.0582646830375</v>
+        <v>198.1945361668876</v>
       </c>
       <c r="W28" t="n">
-        <v>193.6715880782802</v>
+        <v>198.1945361668876</v>
       </c>
       <c r="X28" t="n">
-        <v>193.6715880782802</v>
+        <v>198.1945361668876</v>
       </c>
       <c r="Y28" t="n">
-        <v>193.6715880782802</v>
+        <v>198.1945361668876</v>
       </c>
     </row>
     <row r="29">
@@ -6436,13 +6436,13 @@
         <v>1002.422926871105</v>
       </c>
       <c r="D29" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E29" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F29" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G29" t="n">
         <v>266.2182411146742</v>
@@ -6460,16 +6460,16 @@
         <v>472.6691130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>1379.698607607278</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M29" t="n">
-        <v>1890.547436336213</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N29" t="n">
-        <v>1890.547436336213</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O29" t="n">
-        <v>2843.58998035817</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P29" t="n">
         <v>3629.400904947332</v>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C31" t="n">
-        <v>146.8509448365277</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D31" t="n">
-        <v>146.8509448365277</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E31" t="n">
-        <v>146.8509448365277</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F31" t="n">
-        <v>146.8509448365277</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G31" t="n">
-        <v>146.8509448365277</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H31" t="n">
-        <v>143.0417265520644</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="I31" t="n">
-        <v>190.9246054881473</v>
+        <v>241.5544670143631</v>
       </c>
       <c r="J31" t="n">
-        <v>378.7583461405986</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="K31" t="n">
-        <v>378.7583461405986</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="L31" t="n">
-        <v>378.7583461405986</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="M31" t="n">
-        <v>378.7583461405986</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="N31" t="n">
-        <v>378.7583461405986</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="O31" t="n">
-        <v>378.7583461405986</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="P31" t="n">
-        <v>378.7583461405986</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="Q31" t="n">
         <v>81.36</v>
@@ -6651,13 +6651,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y31" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="32">
@@ -6694,16 +6694,16 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>472.6691130376557</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L32" t="n">
-        <v>1379.698607607278</v>
+        <v>1643.743792536527</v>
       </c>
       <c r="M32" t="n">
-        <v>1814.770397018269</v>
+        <v>2154.592621265462</v>
       </c>
       <c r="N32" t="n">
-        <v>1814.770397018269</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="O32" t="n">
         <v>2767.812941040225</v>
@@ -6718,25 +6718,25 @@
         <v>4041.860001183541</v>
       </c>
       <c r="S32" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T32" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U32" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V32" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W32" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X32" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y32" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="33">
@@ -6767,25 +6767,25 @@
         <v>81.36</v>
       </c>
       <c r="I33" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J33" t="n">
-        <v>428.066520175299</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>840.0093362696824</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L33" t="n">
-        <v>1334.109797864882</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M33" t="n">
-        <v>1642.940339607742</v>
+        <v>1650.735217575307</v>
       </c>
       <c r="N33" t="n">
-        <v>1998.97062421531</v>
+        <v>2006.765502182875</v>
       </c>
       <c r="O33" t="n">
-        <v>2460.763075899029</v>
+        <v>2468.557953866594</v>
       </c>
       <c r="P33" t="n">
         <v>2600.013000882351</v>
@@ -6843,34 +6843,34 @@
         <v>193.6715880782802</v>
       </c>
       <c r="H34" t="n">
-        <v>189.862369793817</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="I34" t="n">
-        <v>237.7452487298999</v>
+        <v>241.5544670143631</v>
       </c>
       <c r="J34" t="n">
-        <v>425.5789893823512</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="K34" t="n">
-        <v>425.5789893823512</v>
+        <v>429.3882076668144</v>
       </c>
       <c r="L34" t="n">
-        <v>425.5789893823512</v>
+        <v>228.8350479114819</v>
       </c>
       <c r="M34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="N34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="O34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q34" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R34" t="n">
         <v>81.36</v>
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I35" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J35" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="K35" t="n">
-        <v>598.13</v>
+        <v>44.8</v>
       </c>
       <c r="L35" t="n">
-        <v>1151.54</v>
+        <v>599.2</v>
       </c>
       <c r="M35" t="n">
-        <v>1243.990904947333</v>
+        <v>1110.048828728935</v>
       </c>
       <c r="N35" t="n">
-        <v>1797.400904947332</v>
+        <v>1110.048828728935</v>
       </c>
       <c r="O35" t="n">
-        <v>1797.400904947332</v>
+        <v>1664.448828728935</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2218.848828728935</v>
       </c>
       <c r="Q35" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R35" t="n">
-        <v>2231.994554156147</v>
+        <v>2240</v>
       </c>
       <c r="S35" t="n">
-        <v>2085.68327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.617029377474</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>407.3842417608302</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C36" t="n">
-        <v>396.1722089875784</v>
+        <v>396.2522089875785</v>
       </c>
       <c r="D36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J36" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K36" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L36" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M36" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N36" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O36" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P36" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X36" t="n">
-        <v>492.1801502582655</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y36" t="n">
-        <v>442.2898545348975</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J37" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K37" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L37" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M37" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N37" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O37" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P37" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q37" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R37" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S37" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C38" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D38" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I38" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J38" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="K38" t="n">
-        <v>598.13</v>
+        <v>181.7520762183974</v>
       </c>
       <c r="L38" t="n">
-        <v>1151.54</v>
+        <v>181.7520762183974</v>
       </c>
       <c r="M38" t="n">
-        <v>1151.54</v>
+        <v>692.6009049473324</v>
       </c>
       <c r="N38" t="n">
-        <v>1704.95</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="O38" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q38" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.68327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.617029377474</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>275.2516144816847</v>
+        <v>402.1454643105373</v>
       </c>
       <c r="C39" t="n">
-        <v>264.0395817084329</v>
+        <v>390.9334315372855</v>
       </c>
       <c r="D39" t="n">
-        <v>264.0395817084329</v>
+        <v>390.9334315372855</v>
       </c>
       <c r="E39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.8</v>
       </c>
       <c r="F39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.8</v>
       </c>
       <c r="G39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.8</v>
       </c>
       <c r="H39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.8</v>
       </c>
       <c r="I39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J39" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K39" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L39" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M39" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N39" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O39" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P39" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>708.3170038559392</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T39" t="n">
-        <v>652.400069292794</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U39" t="n">
-        <v>578.9834316121869</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V39" t="n">
-        <v>513.8211415197422</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W39" t="n">
-        <v>430.6159466613296</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X39" t="n">
-        <v>360.0475229791199</v>
+        <v>486.9413728079726</v>
       </c>
       <c r="Y39" t="n">
-        <v>310.1572272557519</v>
+        <v>437.0510770846046</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400257</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.5478354584615</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.486666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.347639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.254204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.2707901053</v>
       </c>
       <c r="I40" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.903669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K40" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L40" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M40" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N40" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O40" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P40" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q40" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R40" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S40" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248843</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W40" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X40" t="n">
-        <v>745.8791912947012</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737335</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I41" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J41" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="K41" t="n">
-        <v>598.13</v>
+        <v>44.8</v>
       </c>
       <c r="L41" t="n">
-        <v>598.13</v>
+        <v>599.2</v>
       </c>
       <c r="M41" t="n">
-        <v>598.13</v>
+        <v>599.2</v>
       </c>
       <c r="N41" t="n">
-        <v>1151.54</v>
+        <v>1153.6</v>
       </c>
       <c r="O41" t="n">
-        <v>1704.95</v>
+        <v>1708</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q41" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.68327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.617029377474</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J42" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K42" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L42" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M42" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N42" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O42" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T42" t="n">
-        <v>763.9167385504073</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U42" t="n">
-        <v>713.1992034391076</v>
+        <v>713.2792034391077</v>
       </c>
       <c r="V42" t="n">
-        <v>648.0369133466629</v>
+        <v>648.1169133466631</v>
       </c>
       <c r="W42" t="n">
-        <v>564.8317184882503</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>494.2632948060407</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J43" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K43" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L43" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M43" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N43" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O43" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P43" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q43" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R43" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S43" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>435.5410942305735</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>334.0516212578524</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>272.092878086287</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>216.1703633318742</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>159.716192919741</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>104.4057158621489</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I44" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="K44" t="n">
-        <v>598.13</v>
+        <v>44.8</v>
       </c>
       <c r="L44" t="n">
-        <v>1151.54</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="M44" t="n">
-        <v>1662.388828728935</v>
+        <v>576.7999999999998</v>
       </c>
       <c r="N44" t="n">
-        <v>2215.798828728935</v>
+        <v>1131.2</v>
       </c>
       <c r="O44" t="n">
-        <v>2236</v>
+        <v>1685.6</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="Q44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2092.678618381492</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1852.602273201124</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1549.348438303538</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1265.660535104726</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>973.3640947199306</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>727.6248690020843</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>569.8838345897398</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>402.0654643105373</v>
+        <v>111.2420959302646</v>
       </c>
       <c r="C45" t="n">
-        <v>390.8534315372855</v>
+        <v>99.01996214691172</v>
       </c>
       <c r="D45" t="n">
-        <v>390.8534315372855</v>
+        <v>99.01996214691172</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>99.01996214691172</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>99.01996214691172</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72</v>
+        <v>99.01996214691172</v>
       </c>
       <c r="H45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J45" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K45" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L45" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M45" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N45" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O45" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P45" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>999.9558574469404</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>881.2043423311713</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>471.7520542326725</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>420.0244181112718</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>353.8520270087262</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>269.6367311402125</v>
       </c>
       <c r="X45" t="n">
-        <v>486.8613728079725</v>
+        <v>198.0582064479019</v>
       </c>
       <c r="Y45" t="n">
-        <v>436.9710770846045</v>
+        <v>147.1578097144329</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>870.9066123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>946.4186181306686</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1009.247762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1076.586666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1150.457639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1253.374204945902</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1372.4007901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1543.043669041383</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021627</v>
+        <v>1853.637409693834</v>
       </c>
       <c r="K46" t="n">
-        <v>1921.561060958496</v>
+        <v>1913.511843630703</v>
       </c>
       <c r="L46" t="n">
-        <v>1847.270527465789</v>
+        <v>1838.211209127895</v>
       </c>
       <c r="M46" t="n">
-        <v>1674.915364432911</v>
+        <v>1664.845945084916</v>
       </c>
       <c r="N46" t="n">
-        <v>1451.496096481714</v>
+        <v>1440.416576123618</v>
       </c>
       <c r="O46" t="n">
-        <v>1158.116738826143</v>
+        <v>1148.728577510128</v>
       </c>
       <c r="P46" t="n">
-        <v>817.2602768783884</v>
+        <v>806.8620145522718</v>
       </c>
       <c r="Q46" t="n">
-        <v>437.6246542262692</v>
+        <v>426.2162908900516</v>
       </c>
       <c r="R46" t="n">
-        <v>57.21846434631862</v>
+        <v>44.8</v>
       </c>
       <c r="S46" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>182.3856791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>378.4468717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>526.7782646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>648.1791829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>748.7199739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>809.6392746459406</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>404.4874506895348</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>922.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>855.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>455.2478695740924</v>
+        <v>448.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>385.2870600406814</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>535.5499570547582</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,19 +8204,19 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423173</v>
+        <v>930.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>862.2489580698352</v>
+        <v>863.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>439.6923140185369</v>
+        <v>440.6519099781329</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>421.0430062450903</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>369.4444444444444</v>
+        <v>370.4040404040406</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423173</v>
+        <v>930.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698352</v>
+        <v>863.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
@@ -8678,10 +8678,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>220.2344802797121</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,10 +8690,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>870.5779326741233</v>
+        <v>420.4151231603661</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,10 +8912,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>220.2344802797121</v>
+        <v>615.4962106207786</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -9149,7 +9149,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>1032.917105959907</v>
+        <v>490.3759326937771</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>468.5726303445106</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,10 +9386,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>330.7929522621153</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>916.1914086561842</v>
@@ -9398,16 +9398,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>1032.917105959907</v>
+        <v>956.3746420023875</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9635,13 +9635,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O23" t="n">
-        <v>1032.917105959907</v>
+        <v>956.3746420023875</v>
       </c>
       <c r="P23" t="n">
-        <v>174.6210042976508</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>341.6504820397674</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,13 +9875,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>870.5779326741233</v>
+        <v>452.0918908371339</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10103,19 +10103,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
         <v>1032.917105959907</v>
       </c>
       <c r="P29" t="n">
-        <v>794.0354687166035</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10337,19 +10337,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>916.1914086561842</v>
+        <v>466.0285991424271</v>
       </c>
       <c r="M32" t="n">
-        <v>983.728581592813</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
         <v>870.5779326741233</v>
@@ -10574,25 +10574,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>559.0000000000001</v>
+        <v>560</v>
       </c>
       <c r="M35" t="n">
-        <v>637.6468801143703</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>194.1875037932075</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,19 +10811,19 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="L38" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>163.6326220461452</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11048,22 +11048,22 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="M41" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>629.2478695740924</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P41" t="n">
-        <v>93.67181251273462</v>
+        <v>94.63140847233039</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11285,22 +11285,22 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>559.0000000000001</v>
+        <v>21.36481946572204</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>90.65309308021877</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q44" t="n">
         <v>172.8226843274854</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.591170646055957</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22715,7 +22715,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.209142488276314</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23396,7 +23396,7 @@
         <v>49.38285596774193</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
         <v>3.77112610161862</v>
@@ -23411,10 +23411,10 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>148.2585041314731</v>
       </c>
       <c r="N13" t="n">
         <v>346.1850752716849</v>
@@ -23426,7 +23426,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>471.9668250795317</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
         <v>501.6021279811511</v>
@@ -23444,7 +23444,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
         <v>22.44364543010755</v>
@@ -23636,7 +23636,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H16" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23660,7 +23660,7 @@
         <v>415.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>253.9006416022769</v>
+        <v>120.2982880010401</v>
       </c>
       <c r="Q16" t="n">
         <v>500.839266425598</v>
@@ -23669,7 +23669,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L19" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>295.6316114025499</v>
@@ -23894,19 +23894,19 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>208.2711181917241</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P19" t="n">
         <v>462.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>500.839266425598</v>
+        <v>415.9315120039836</v>
       </c>
       <c r="R19" t="n">
         <v>501.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23918,13 +23918,13 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X19" t="n">
         <v>22.44364543010755</v>
       </c>
       <c r="Y19" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -24125,7 +24125,7 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>346.1850752716849</v>
@@ -24134,10 +24134,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>116.5271618994215</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>500.839266425598</v>
+        <v>451.9229522380016</v>
       </c>
       <c r="R22" t="n">
         <v>501.6021279811511</v>
@@ -24155,7 +24155,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>22.44364543010755</v>
@@ -24347,7 +24347,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H25" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -24365,7 +24365,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>346.1850752716849</v>
+        <v>67.87362863261967</v>
       </c>
       <c r="O25" t="n">
         <v>415.445564079015</v>
@@ -24377,7 +24377,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>157.0542023910048</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>137.3734797028554</v>
@@ -24398,7 +24398,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y25" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -24566,22 +24566,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.11380033707866</v>
+        <v>63.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>55.98090483695654</v>
+        <v>56.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>50.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>20.04387284153003</v>
+        <v>21.04387284153003</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -24593,31 +24593,31 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>63.52077380114304</v>
+        <v>64.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>199.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>296.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>346.1850752716849</v>
+        <v>347.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>415.445564079015</v>
+        <v>416.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>462.4478973282775</v>
+        <v>463.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>160.0624669370703</v>
+        <v>501.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>276.6144833575138</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>138.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24629,13 +24629,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.372809838709685</v>
       </c>
       <c r="X28" t="n">
-        <v>22.44364543010755</v>
+        <v>23.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>62.46535284946236</v>
+        <v>63.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -24806,7 +24806,7 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
         <v>60.53621805555548</v>
@@ -24821,7 +24821,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24848,7 +24848,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>206.4149037464053</v>
+        <v>156.2913408354518</v>
       </c>
       <c r="R31" t="n">
         <v>501.6021279811511</v>
@@ -24866,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>22.44364543010755</v>
@@ -25058,7 +25058,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -25070,10 +25070,10 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L34" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>295.6316114025499</v>
+        <v>149.6313139701828</v>
       </c>
       <c r="N34" t="n">
         <v>346.1850752716849</v>
@@ -25088,7 +25088,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>137.3734797028554</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>6.153808614585273</v>
       </c>
     </row>
     <row r="45">
@@ -26027,7 +26027,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.674445451659892</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>13.37347970285543</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1157099.39426644</v>
+        <v>1156197.973636137</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2259020.889973892</v>
+        <v>2258531.104533217</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3360942.385681347</v>
+        <v>3360486.014824239</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4430585.044896967</v>
+        <v>4430081.396464102</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5470348.2762338</v>
+        <v>5469844.627800935</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6510111.507570631</v>
+        <v>6509607.859137765</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7549874.738907459</v>
+        <v>7549371.090474593</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8589637.970244287</v>
+        <v>8589134.321811423</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9629401.201581115</v>
+        <v>9628773.863254311</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10669164.43291794</v>
+        <v>10668158.87398508</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11708927.66425477</v>
+        <v>11707922.1053219</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12789229.44484883</v>
+        <v>12788271.16349172</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13891184.35513986</v>
+        <v>13890226.07378275</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14993139.26543088</v>
+        <v>14992180.98407377</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16095094.17572191</v>
+        <v>16093370.27516655</v>
       </c>
     </row>
   </sheetData>
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1101921.495707453</v>
+        <v>1101351.018107454</v>
       </c>
       <c r="C2" t="n">
-        <v>1101921.495707453</v>
+        <v>1101954.910291021</v>
       </c>
       <c r="D2" t="n">
-        <v>1101921.495707454</v>
+        <v>1101954.910291021</v>
       </c>
       <c r="E2" t="n">
         <v>1039763.231336833</v>
@@ -26284,7 +26284,7 @@
         <v>1039763.231336833</v>
       </c>
       <c r="G2" t="n">
-        <v>1039763.231336832</v>
+        <v>1039763.231336833</v>
       </c>
       <c r="H2" t="n">
         <v>1039763.231336833</v>
@@ -26293,7 +26293,7 @@
         <v>1039763.231336833</v>
       </c>
       <c r="J2" t="n">
-        <v>1039763.231336833</v>
+        <v>1039261.320836833</v>
       </c>
       <c r="K2" t="n">
         <v>1039763.231336832</v>
@@ -26305,13 +26305,13 @@
         <v>1101954.910291021</v>
       </c>
       <c r="N2" t="n">
-        <v>1101954.910291021</v>
+        <v>1101954.91029102</v>
       </c>
       <c r="O2" t="n">
         <v>1101954.910291021</v>
       </c>
       <c r="P2" t="n">
-        <v>1101954.91029102</v>
+        <v>1101189.29109277</v>
       </c>
     </row>
     <row r="3">
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135520</v>
+        <v>133056</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2816</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>402464</v>
+        <v>402112</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>315520</v>
+        <v>315072</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>180000</v>
+        <v>179200</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572929.6260477751</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570269.0362327077</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.3728533789</v>
+        <v>568208.8854605397</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>448189.3974235593</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482317</v>
+        <v>446735.8466599294</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>445280.2900507811</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>443822.7132121192</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608352</v>
+        <v>442363.1015725328</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>439627.9409972944</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464519</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476346</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529098.4702101597</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072474</v>
+        <v>527134.2939863527</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525167.2765823142</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>522722.0733626525</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57035.6</v>
+        <v>56610</v>
       </c>
       <c r="C5" t="n">
-        <v>57035.6</v>
+        <v>57096.39999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>57035.6</v>
+        <v>57096.39999999999</v>
       </c>
       <c r="E5" t="n">
         <v>80749.125</v>
@@ -26449,7 +26449,7 @@
         <v>80749.125</v>
       </c>
       <c r="J5" t="n">
-        <v>80749.125</v>
+        <v>81151.45600000001</v>
       </c>
       <c r="K5" t="n">
         <v>80749.125</v>
@@ -26458,16 +26458,16 @@
         <v>80749.125</v>
       </c>
       <c r="M5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="N5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="O5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="P5" t="n">
-        <v>63411.35</v>
+        <v>63388.08100000001</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>338451.7708079444</v>
+        <v>338755.3920596784</v>
       </c>
       <c r="C6" t="n">
-        <v>476029.7509417586</v>
+        <v>471773.4740583128</v>
       </c>
       <c r="D6" t="n">
-        <v>478090.5228540748</v>
+        <v>476649.624830481</v>
       </c>
       <c r="E6" t="n">
-        <v>110697.416824971</v>
+        <v>108712.7089132732</v>
       </c>
       <c r="F6" t="n">
-        <v>514614.9675886008</v>
+        <v>512278.2596769031</v>
       </c>
       <c r="G6" t="n">
-        <v>516070.5241977489</v>
+        <v>513733.8162860514</v>
       </c>
       <c r="H6" t="n">
-        <v>517528.101036411</v>
+        <v>515191.3931247137</v>
       </c>
       <c r="I6" t="n">
-        <v>518987.7126759973</v>
+        <v>516651.0047643</v>
       </c>
       <c r="J6" t="n">
-        <v>204929.37387889</v>
+        <v>203409.9238395384</v>
       </c>
       <c r="K6" t="n">
-        <v>521913.0996020782</v>
+        <v>518776.3916903805</v>
       </c>
       <c r="L6" t="n">
-        <v>523378.9050008956</v>
+        <v>521042.1970891978</v>
       </c>
       <c r="M6" t="n">
-        <v>349820.8357489199</v>
+        <v>348136.2900808608</v>
       </c>
       <c r="N6" t="n">
-        <v>513033.7327837731</v>
+        <v>511348.4663046675</v>
       </c>
       <c r="O6" t="n">
-        <v>335001.4720415114</v>
+        <v>334115.4837087063</v>
       </c>
       <c r="P6" t="n">
-        <v>516972.0748925213</v>
+        <v>515079.1367301173</v>
       </c>
     </row>
   </sheetData>
@@ -26779,7 +26779,7 @@
         <v>225</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" t="n">
         <v>225</v>
@@ -26797,7 +26797,7 @@
         <v>350</v>
       </c>
       <c r="P2" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3">
@@ -26859,13 +26859,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E4" t="n">
         <v>1017</v>
@@ -26883,7 +26883,7 @@
         <v>1017</v>
       </c>
       <c r="J4" t="n">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="K4" t="n">
         <v>1017</v>
@@ -26892,16 +26892,16 @@
         <v>1017</v>
       </c>
       <c r="M4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -26972,34 +26972,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>225</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27008,13 +27008,13 @@
         <v>125</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -27036,7 +27036,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -27048,25 +27048,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -27076,49 +27076,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27228,10 +27228,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -27317,16 +27317,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>222.1724074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>398.4594086145854</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>7.616740135105431</v>
+        <v>204.2843561227035</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27575,7 +27575,7 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>47.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27597,22 +27597,22 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F4" t="n">
+        <v>384.8494534278994</v>
+      </c>
+      <c r="G4" t="n">
         <v>400</v>
       </c>
-      <c r="F4" t="n">
-        <v>274.3828559677419</v>
-      </c>
-      <c r="G4" t="n">
-        <v>245.04387284153</v>
-      </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>323.1566159682502</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
@@ -27645,22 +27645,22 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27676,7 +27676,7 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="E5" t="n">
         <v>400</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>218.2916074428799</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27764,7 +27764,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27800,16 +27800,16 @@
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>306.9166103990634</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>20.35776521751382</v>
+        <v>239.5032443000844</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>28.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27834,19 +27834,19 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>261.4340159791818</v>
       </c>
       <c r="I7" t="n">
         <v>176.6334556201183</v>
@@ -27855,7 +27855,7 @@
         <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T7" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U7" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V7" t="n">
         <v>400</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>400</v>
       </c>
-      <c r="U7" t="n">
-        <v>400</v>
-      </c>
-      <c r="V7" t="n">
-        <v>259.0245120334699</v>
-      </c>
-      <c r="W7" t="n">
-        <v>226.3728098387097</v>
-      </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27910,7 +27910,7 @@
         <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>117.4941682972701</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -28004,7 +28004,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28037,22 +28037,22 @@
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>277.9009689796695</v>
+        <v>80.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>193.8784628383869</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>29.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>34.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28071,16 +28071,16 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E10" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F10" t="n">
         <v>400</v>
       </c>
-      <c r="E10" t="n">
-        <v>400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>274.3828559677419</v>
-      </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
         <v>400</v>
@@ -28092,7 +28092,7 @@
         <v>400</v>
       </c>
       <c r="K10" t="n">
-        <v>288.520773801143</v>
+        <v>394.441636588982</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T10" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
-      </c>
-      <c r="T10" t="n">
-        <v>396.5206623753519</v>
-      </c>
-      <c r="U10" t="n">
-        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
+        <v>247.4436454301076</v>
+      </c>
+      <c r="Y10" t="n">
         <v>400</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>225</v>
       </c>
       <c r="I11" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28213,7 +28213,7 @@
         <v>225</v>
       </c>
       <c r="Y11" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12">
@@ -28244,13 +28244,13 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>19.11687125883913</v>
+        <v>78.91122027701095</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28268,7 +28268,7 @@
         <v>225</v>
       </c>
       <c r="Q12" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
         <v>225</v>
@@ -28399,10 +28399,10 @@
         <v>225</v>
       </c>
       <c r="H14" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28481,10 +28481,10 @@
         <v>225</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J15" t="n">
-        <v>225</v>
+        <v>71.03760616835949</v>
       </c>
       <c r="K15" t="n">
         <v>225</v>
@@ -28502,7 +28502,7 @@
         <v>225</v>
       </c>
       <c r="P15" t="n">
-        <v>78.91122027701083</v>
+        <v>225</v>
       </c>
       <c r="Q15" t="n">
         <v>173.0792650904796</v>
@@ -28633,7 +28633,7 @@
         <v>225</v>
       </c>
       <c r="G17" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="H17" t="n">
         <v>225</v>
@@ -28669,7 +28669,7 @@
         <v>225</v>
       </c>
       <c r="S17" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="T17" t="n">
         <v>225</v>
@@ -28718,10 +28718,10 @@
         <v>225</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J18" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K18" t="n">
         <v>225</v>
@@ -28733,7 +28733,7 @@
         <v>225</v>
       </c>
       <c r="N18" t="n">
-        <v>26.99048536749072</v>
+        <v>225</v>
       </c>
       <c r="O18" t="n">
         <v>225</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="S20" t="n">
         <v>225</v>
@@ -28915,7 +28915,7 @@
         <v>225</v>
       </c>
       <c r="V20" t="n">
-        <v>219.5068074428799</v>
+        <v>225</v>
       </c>
       <c r="W20" t="n">
         <v>225</v>
@@ -28955,19 +28955,19 @@
         <v>225</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J21" t="n">
         <v>225</v>
       </c>
       <c r="K21" t="n">
-        <v>26.99048536749061</v>
+        <v>225</v>
       </c>
       <c r="L21" t="n">
         <v>225</v>
       </c>
       <c r="M21" t="n">
-        <v>225</v>
+        <v>19.11687125883903</v>
       </c>
       <c r="N21" t="n">
         <v>225</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="S23" t="n">
         <v>225</v>
@@ -29158,7 +29158,7 @@
         <v>225</v>
       </c>
       <c r="X23" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="Y23" t="n">
         <v>225</v>
@@ -29192,7 +29192,7 @@
         <v>225</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J24" t="n">
         <v>225</v>
@@ -29204,13 +29204,13 @@
         <v>225</v>
       </c>
       <c r="M24" t="n">
-        <v>26.99048536749062</v>
+        <v>225</v>
       </c>
       <c r="N24" t="n">
         <v>225</v>
       </c>
       <c r="O24" t="n">
-        <v>225</v>
+        <v>19.11687125883898</v>
       </c>
       <c r="P24" t="n">
         <v>225</v>
@@ -29329,25 +29329,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C26" t="n">
-        <v>219.5068074428802</v>
+        <v>224</v>
       </c>
       <c r="D26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G26" t="n">
-        <v>225</v>
+        <v>202.4604074428802</v>
       </c>
       <c r="H26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I26" t="n">
         <v>150.0811596826846</v>
@@ -29377,28 +29377,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27">
@@ -29408,76 +29408,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I27" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K27" t="n">
-        <v>225</v>
+        <v>49.29504612659639</v>
       </c>
       <c r="L27" t="n">
-        <v>19.11687125883913</v>
+        <v>224</v>
       </c>
       <c r="M27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28">
@@ -29487,76 +29487,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29">
@@ -29572,7 +29572,7 @@
         <v>225</v>
       </c>
       <c r="D29" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="E29" t="n">
         <v>225</v>
@@ -29581,7 +29581,7 @@
         <v>225</v>
       </c>
       <c r="G29" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="H29" t="n">
         <v>225</v>
@@ -29803,7 +29803,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="C32" t="n">
         <v>225</v>
@@ -29854,7 +29854,7 @@
         <v>225</v>
       </c>
       <c r="S32" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="T32" t="n">
         <v>225</v>
@@ -29903,7 +29903,7 @@
         <v>225</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J33" t="n">
         <v>225</v>
@@ -29924,7 +29924,7 @@
         <v>225</v>
       </c>
       <c r="P33" t="n">
-        <v>26.99048536749045</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q33" t="n">
         <v>225</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30122,7 +30122,7 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>285.2599243722599</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -30185,7 +30185,7 @@
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>285.2599243722601</v>
+        <v>350</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30328,7 +30328,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30365,7 +30365,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30377,7 +30377,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>350</v>
@@ -30413,7 +30413,7 @@
         <v>350</v>
       </c>
       <c r="U39" t="n">
-        <v>327.5278884563857</v>
+        <v>350</v>
       </c>
       <c r="V39" t="n">
         <v>350</v>
@@ -30422,7 +30422,7 @@
         <v>350</v>
       </c>
       <c r="X39" t="n">
-        <v>350</v>
+        <v>279.9943346964699</v>
       </c>
       <c r="Y39" t="n">
         <v>350</v>
@@ -30459,7 +30459,7 @@
         <v>350</v>
       </c>
       <c r="J40" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="K40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30523,7 +30523,7 @@
         <v>350</v>
       </c>
       <c r="E41" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="F41" t="n">
         <v>350</v>
@@ -30565,7 +30565,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T41" t="n">
         <v>350</v>
@@ -30647,22 +30647,22 @@
         <v>350</v>
       </c>
       <c r="T42" t="n">
+        <v>350</v>
+      </c>
+      <c r="U42" t="n">
         <v>287.3222374745575</v>
-      </c>
-      <c r="U42" t="n">
-        <v>350</v>
       </c>
       <c r="V42" t="n">
         <v>350</v>
       </c>
       <c r="W42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30751,28 +30751,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30802,25 +30802,25 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="U44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45">
@@ -30830,16 +30830,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>339.6362423378769</v>
@@ -30848,7 +30848,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>332.1680871864211</v>
+        <v>278.4903246609786</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30878,28 +30878,28 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="S45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X45" t="n">
-        <v>279.99433469647</v>
+        <v>349</v>
       </c>
       <c r="Y45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="M46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="S46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>349</v>
       </c>
       <c r="U46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34752,19 +34752,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="O2" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="P2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>362.7272727272729</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34883,22 +34883,22 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>110.4665974601575</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>146.5231603481319</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -34931,22 +34931,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,19 +34983,19 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O5" t="n">
-        <v>369.4444444444445</v>
+        <v>370.4040404040405</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -35120,19 +35120,19 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>32.66288987756318</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -35141,7 +35141,7 @@
         <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,22 +35165,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>59.85420181725371</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>369.4444444444444</v>
+        <v>370.4040404040406</v>
       </c>
       <c r="M8" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N8" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35357,16 +35357,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>171.2288738983814</v>
@@ -35378,7 +35378,7 @@
         <v>364.7310511640923</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>105.920862787839</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>186.4960958690942</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L11" t="n">
-        <v>220.2344802797121</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,10 +35469,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>870.2908726334418</v>
+        <v>420.1280631196846</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35530,13 +35530,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>210.2207258996305</v>
+        <v>270.0150749178023</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35554,7 +35554,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35691,10 +35691,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>220.2344802797121</v>
+        <v>615.4962106207786</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -35767,10 +35767,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J15" t="n">
-        <v>350.2086062376757</v>
+        <v>196.2462124060352</v>
       </c>
       <c r="K15" t="n">
         <v>416.1038546407913</v>
@@ -35788,7 +35788,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>192.577224791664</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>962.6692363858147</v>
+        <v>420.1280631196846</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>295.7499460170251</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,10 +36004,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J18" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K18" t="n">
         <v>416.1038546407913</v>
@@ -36019,7 +36019,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N18" t="n">
-        <v>161.6170354761456</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O18" t="n">
         <v>466.4570219027464</v>
@@ -36165,10 +36165,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>295.7499460170249</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>916.1914086561842</v>
@@ -36177,16 +36177,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>962.6692363858147</v>
+        <v>886.126772428295</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36241,19 +36241,19 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J21" t="n">
         <v>350.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>218.0943400082819</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>499.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233433</v>
       </c>
       <c r="N21" t="n">
         <v>359.6265501086548</v>
@@ -36414,13 +36414,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>962.6692363858147</v>
+        <v>886.126772428295</v>
       </c>
       <c r="P23" t="n">
-        <v>174.3339442569694</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36478,7 +36478,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J24" t="n">
         <v>350.2086062376757</v>
@@ -36490,13 +36490,13 @@
         <v>499.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>113.9405275319949</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N24" t="n">
         <v>359.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615854</v>
       </c>
       <c r="P24" t="n">
         <v>338.6660045146532</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
         <v>716.8751175230993</v>
       </c>
       <c r="L26" t="n">
-        <v>341.6504820397674</v>
+        <v>916.191408656184</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,13 +36654,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>870.2908726334418</v>
+        <v>451.8048307964524</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,31 +36715,31 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>350.2086062376757</v>
+        <v>349.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>416.1038546407913</v>
+        <v>240.3989007673877</v>
       </c>
       <c r="L27" t="n">
-        <v>293.2082466075261</v>
+        <v>498.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>311.9500421645043</v>
+        <v>310.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>359.6265501086548</v>
+        <v>358.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>466.4570219027464</v>
+        <v>465.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>337.6660045146532</v>
       </c>
       <c r="Q27" t="n">
-        <v>51.92073490952041</v>
+        <v>50.92073490952041</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36794,10 +36794,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>48.36654437988173</v>
+        <v>47.36654437988173</v>
       </c>
       <c r="J28" t="n">
-        <v>189.7310511640922</v>
+        <v>188.7310511640922</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -36827,13 +36827,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>14.97543349374229</v>
+        <v>13.97543349374229</v>
       </c>
       <c r="U28" t="n">
-        <v>74.04160872554206</v>
+        <v>73.04160872554206</v>
       </c>
       <c r="V28" t="n">
-        <v>25.82968978378381</v>
+        <v>24.82968978378381</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -36882,19 +36882,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
         <v>962.6692363858147</v>
       </c>
       <c r="P29" t="n">
-        <v>793.7484086759221</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -37116,19 +37116,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L32" t="n">
-        <v>916.1914086561842</v>
+        <v>466.0285991424271</v>
       </c>
       <c r="M32" t="n">
-        <v>439.4664539504957</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>870.2908726334418</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J33" t="n">
         <v>350.2086062376757</v>
@@ -37210,7 +37210,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>140.6564898821437</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q33" t="n">
         <v>51.92073490952041</v>
@@ -37353,25 +37353,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>559.0000000000001</v>
+        <v>560</v>
       </c>
       <c r="M35" t="n">
-        <v>93.38475247205298</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>21.36481946572209</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37590,19 +37590,19 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="L38" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O38" t="n">
-        <v>93.38475247205275</v>
+        <v>560</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J40" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982266</v>
       </c>
       <c r="K40" t="n">
         <v>61.47922619885696</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37827,22 +37827,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O41" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P41" t="n">
-        <v>93.38475247205321</v>
+        <v>94.34434843164898</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38064,22 +38064,22 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>559.0000000000001</v>
+        <v>21.36481946572204</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O44" t="n">
-        <v>20.40522350612631</v>
+        <v>560</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38195,34 +38195,34 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>62.88619966292134</v>
+        <v>61.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>77.27475335195533</v>
+        <v>76.27475335195533</v>
       </c>
       <c r="D46" t="n">
-        <v>64.46378194444452</v>
+        <v>63.46378194444452</v>
       </c>
       <c r="E46" t="n">
-        <v>69.01909516304346</v>
+        <v>68.01909516304346</v>
       </c>
       <c r="F46" t="n">
-        <v>75.61714403225807</v>
+        <v>74.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>104.95612715847</v>
+        <v>103.95612715847</v>
       </c>
       <c r="H46" t="n">
-        <v>121.2288738983814</v>
+        <v>120.2288738983814</v>
       </c>
       <c r="I46" t="n">
-        <v>173.3665443798817</v>
+        <v>172.3665443798817</v>
       </c>
       <c r="J46" t="n">
-        <v>314.7310511640923</v>
+        <v>313.7310511640923</v>
       </c>
       <c r="K46" t="n">
-        <v>61.47922619885696</v>
+        <v>60.47922619885696</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,22 +38249,22 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>138.9754334937423</v>
       </c>
       <c r="U46" t="n">
-        <v>199.0416087255421</v>
+        <v>198.0416087255421</v>
       </c>
       <c r="V46" t="n">
-        <v>150.8296897837838</v>
+        <v>149.8296897837838</v>
       </c>
       <c r="W46" t="n">
-        <v>123.6271901612903</v>
+        <v>122.6271901612903</v>
       </c>
       <c r="X46" t="n">
-        <v>102.5563545698924</v>
+        <v>101.5563545698924</v>
       </c>
       <c r="Y46" t="n">
-        <v>62.53464715053764</v>
+        <v>61.53464715053764</v>
       </c>
     </row>
   </sheetData>
